--- a/consolidacion/data/pruebas/personas_gestion_riesgo_20260814_0800.xlsx
+++ b/consolidacion/data/pruebas/personas_gestion_riesgo_20260814_0800.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
